--- a/data/trans_bre/IP19C04-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP19C04-Estudios-trans_bre.xlsx
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,19; 2,47</t>
+          <t>-16,79; 2,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 18,57</t>
+          <t>-0,14; 18,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 18,1</t>
+          <t>-2,72; 17,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 4,5</t>
+          <t>-12,63; 4,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-89,99; 74,96</t>
+          <t>-90,42; 78,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-41,04; 1111,87</t>
+          <t>-30,43; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 3,26</t>
+          <t>-4,36; 2,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 3,26</t>
+          <t>-4,49; 3,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 4,0</t>
+          <t>-2,04; 4,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 5,27</t>
+          <t>-1,26; 4,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-47,76; 68,39</t>
+          <t>-50,78; 62,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-47,82; 63,46</t>
+          <t>-50,04; 67,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,45; 127,26</t>
+          <t>-35,94; 142,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-27,66; 267,63</t>
+          <t>-32,11; 205,41</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 5,17</t>
+          <t>-7,43; 5,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 2,13</t>
+          <t>-5,76; 2,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 5,65</t>
+          <t>-3,59; 6,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 6,63</t>
+          <t>-1,79; 6,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-78,61; 237,61</t>
+          <t>-78,69; 205,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 338,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-83,03; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-61,52; 845,66</t>
+          <t>-54,16; 769,98</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 1,87</t>
+          <t>-4,14; 1,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 3,84</t>
+          <t>-2,24; 3,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 4,03</t>
+          <t>-1,13; 3,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 4,14</t>
+          <t>-0,88; 3,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-47,95; 32,59</t>
+          <t>-47,21; 37,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-33,33; 83,87</t>
+          <t>-32,55; 80,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-25,25; 159,24</t>
+          <t>-23,29; 138,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,39; 191,18</t>
+          <t>-25,33; 155,73</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C04-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP19C04-Estudios-trans_bre.xlsx
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,79; 2,17</t>
+          <t>-17,01; 2,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 18,86</t>
+          <t>-0,17; 18,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 17,14</t>
+          <t>-2,48; 18,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 4,99</t>
+          <t>-12,45; 4,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-90,42; 78,66</t>
+          <t>-91,33; 85,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-30,43; —</t>
+          <t>-35,36; 1125,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 2,99</t>
+          <t>-4,25; 2,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 3,37</t>
+          <t>-4,16; 3,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 4,38</t>
+          <t>-1,79; 4,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 4,88</t>
+          <t>-1,15; 4,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-50,78; 62,11</t>
+          <t>-50,03; 60,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-50,04; 67,71</t>
+          <t>-48,88; 87,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-35,94; 142,89</t>
+          <t>-32,56; 138,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,11; 205,41</t>
+          <t>-28,65; 215,68</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 5,28</t>
+          <t>-6,76; 5,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 2,03</t>
+          <t>-5,89; 2,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 6,12</t>
+          <t>-3,42; 6,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 6,63</t>
+          <t>-2,64; 5,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-78,69; 205,67</t>
+          <t>-75,02; 253,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-83,03; —</t>
+          <t>-83,92; 744,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-54,16; 769,98</t>
+          <t>-70,29; 635,38</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 1,77</t>
+          <t>-4,3; 1,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 3,57</t>
+          <t>-2,29; 3,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 3,84</t>
+          <t>-0,99; 4,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 3,88</t>
+          <t>-0,87; 3,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-47,21; 37,09</t>
+          <t>-49,46; 38,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,55; 80,41</t>
+          <t>-31,09; 93,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,29; 138,22</t>
+          <t>-20,74; 158,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,33; 155,73</t>
+          <t>-23,85; 168,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C04-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP19C04-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,39</t>
+          <t>-2,19</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-49,93%</t>
+          <t>-46,4%</t>
         </is>
       </c>
     </row>
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,01; 2,48</t>
+          <t>-17,19; 2,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 18,38</t>
+          <t>-0,36; 18,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 18,47</t>
+          <t>-2,67; 18,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 4,47</t>
+          <t>-15,65; 4,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-91,33; 85,53</t>
+          <t>-89,99; 74,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-35,36; 1125,18</t>
+          <t>-41,04; 1111,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,72</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>43,82%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 2,89</t>
+          <t>-4,03; 3,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 3,8</t>
+          <t>-4,05; 3,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 4,61</t>
+          <t>-2,41; 4,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 4,88</t>
+          <t>-1,14; 4,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-50,03; 60,49</t>
+          <t>-47,76; 68,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-48,88; 87,01</t>
+          <t>-47,82; 63,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-32,56; 138,61</t>
+          <t>-42,45; 127,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,65; 215,68</t>
+          <t>-29,79; 246,12</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,77</t>
+          <t>1,52</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>56,33%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 5,37</t>
+          <t>-7,31; 5,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 2,08</t>
+          <t>-5,8; 2,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 6,08</t>
+          <t>-3,61; 5,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 5,92</t>
+          <t>-2,31; 6,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-75,02; 253,44</t>
+          <t>-78,61; 237,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 338,64</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-83,92; 744,13</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-70,29; 635,38</t>
+          <t>-62,42; 812,08</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,47</t>
+          <t>1,22</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>38,85%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 1,9</t>
+          <t>-4,16; 1,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 3,86</t>
+          <t>-2,37; 3,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 4,07</t>
+          <t>-1,23; 4,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 3,76</t>
+          <t>-0,81; 3,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,46; 38,85</t>
+          <t>-47,95; 32,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,09; 93,91</t>
+          <t>-33,33; 83,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-20,74; 158,49</t>
+          <t>-25,25; 159,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,85; 168,21</t>
+          <t>-21,22; 171,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C04-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP19C04-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,191 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-5,83</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8,93</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5,78</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-2,19</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-51,74%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>192,72%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>223,85%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-46,4%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-5.832918180963284</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>8.928224692819162</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>5.779440252384458</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-2.187988521222286</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.5173982252554797</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>1.927191020581355</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>2.238494268488375</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.4640308027582437</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-17,19; 2,47</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-0,36; 18,57</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-2,67; 18,1</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-15,65; 4,73</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-89,99; 74,96</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-41,04; 1111,87</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-17.1851566222941</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-0.36373411954678</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-2.671841501034009</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-15.651982173102</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.8999332672054419</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.4103677394988155</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2.470101518149771</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>18.57271167122101</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>18.09745295893959</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>4.731750414245731</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.7495688354639065</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>11.11868283930261</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,6</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,29</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,12</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,4</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-8,9%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-4,31%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>24,8%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>43,82%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-4,03; 3,26</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-4,05; 3,26</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-2,41; 4,0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-1,14; 4,5</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-47,76; 68,39</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-47,82; 63,46</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-42,45; 127,26</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-29,79; 246,12</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.5961131502846745</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.2898641596332616</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.115580057170257</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1.396234736347969</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.08898422245196012</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.04306854786337525</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.2479709480308924</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.4382331693903522</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,58</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-1,61</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,85</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,52</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-9,89%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-47,53%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>31,74%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>56,33%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-4.026754955848734</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-4.046331627285396</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.405097286206363</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-1.139411329210624</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.4776087098350146</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.478234636703899</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.4244538899072353</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.2979151408966521</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-7,31; 5,17</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-5,8; 2,13</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-3,61; 5,65</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-2,31; 6,35</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-78,61; 237,61</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 338,64</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-62,42; 812,08</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3.264754345736366</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3.25536430935224</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.998648213043569</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>4.502384780791511</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.68390215153481</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.6346464073517403</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1.272585205928928</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>2.461204793665683</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +811,193 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,24</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,55</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,36</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,22</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-17,44%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,51%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>34,77%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>38,85%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.5845827071031644</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-1.605381902369399</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.8488551757027331</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.516448387169871</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.09888252806432053</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.4753082798949701</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.3174314667744279</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.5633205896355685</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-4,16; 1,87</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,37; 3,84</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-1,23; 4,03</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-0,81; 3,58</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-47,95; 32,59</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-33,33; 83,87</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-25,25; 159,24</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-21,22; 171,28</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-7.305703818606982</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-5.800417879398071</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-3.611579786735403</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-2.314142365094352</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.7860584628801141</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="n">
+        <v>-0.6242455422748678</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>5.170589661131961</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2.129316666108204</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5.653091976533457</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>6.351920006937008</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>2.376055943648437</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>3.386399035514536</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="n">
+        <v>8.120825766249126</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-1.235242497071801</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.5453006366582815</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.362606974750614</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1.216152037853348</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1744109336921355</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.0951364782534824</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.34774439796187</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.3885164540476794</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-4.161618589533731</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.373066499499445</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.231865662351328</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-0.8130009150433019</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.4795010610618686</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.3332610507823771</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.2525376437117592</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.2121568885810222</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.871085736648567</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3.836824682774568</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>4.026638860049214</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>3.580337996178403</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.3259357150565209</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.8387175221282953</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1.592412537469209</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>1.712822171241668</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1005,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
